--- a/Test Cases - Restful-Book-API Testing.xlsx
+++ b/Test Cases - Restful-Book-API Testing.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/645d61d5e96f01f8/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{BE8F75D9-A0CE-4ED7-9DE4-348E307106D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0FB74BA5-4D33-4C6B-B097-1E7ADF0D722A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{828A7321-3413-4137-9BF2-3204B351D12E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{350147D6-CFBF-4A36-87AD-04660AEB71D6}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="154">
   <si>
     <t>Scenario TID</t>
   </si>
@@ -654,48 +654,6 @@
 </t>
   </si>
   <si>
-    <t>Verify if the user is not able to do partial update using PUT request</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.Login to POSTMAN tool
-2.Import the curl command using raw text format
-curl -X PUT \
-https://restful-booker.herokuapp.com/booking/1 \
--H 'Content-Type: application/json' \
--H 'Accept: application/json' \
--H 'Cookie: token=abc123' \
--d '{
-"firstname" : "James",
-"lastname" : "Brown",
-"totalprice" : 111,
-// "depositpaid" : true,
-"bookingdates" : {
-"checkin" : "2018-01-01",
-"checkout" : "2019-01-01"
-},
-"additionalneeds" : "Breakfast"
-}'
-3.Click send request button.Verify if user is not able to successfully update 
-the booking
-POSTMAN Scripting:
-pm.test("Status code is 400", function () {
-pm.response.to.have.status(400);
-});
-pm.test("Status code name has string", function () {
-pm.response.to.have.status("Bad Request");
-});
-</t>
-  </si>
-  <si>
-    <t>1.Sucessful login
-2.Import request successful
-3.The user must not be able to update the resource bookingid
-and response statuscode must be 400 bad request</t>
-  </si>
-  <si>
-    <t>Verify the status code that user gets for trying Partial update using PUT request</t>
-  </si>
-  <si>
     <t>.Verify if user is able to delete all bookings</t>
   </si>
   <si>
@@ -949,6 +907,136 @@
   </si>
   <si>
     <t>123niroj</t>
+  </si>
+  <si>
+    <t>Execute API request and verify response</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The API must fetch all bookings
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response body must show list of all bookings
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Status code must be 404 for all booking deleted
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Status code must be 200 for all booking deleted
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.Successful action and The Response time must be less than 200ms
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The API must fetch the single booking which you requested
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response body must show the booking requested
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response code must be 404</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response code must be 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response must be
+{
+"bookingid": 1,
+"booking": {
+"firstname": "Jim",
+"lastname": "Brown",
+"totalprice": 111,
+"depositpaid": true,
+"bookingdates": {
+"checkin": "2018-01-01",
+"checkout": "2019-01-01"
+},
+"additionalneeds": "Breakfast"
+}
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response code must be 200 
+and response body must be
+HTTP/1.1 200 OK
+{
+"firstname" : "James",
+"lastname" : "Brown",
+"totalprice" : 111,
+"depositpaid" : true,
+"bookingdates" : {
+"checkin" : "2018-01-01",
+"checkout" : "2019-01-01"
+},
+"additionalneeds" : "Breakfast"
+}</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response code must be 200 
+and response header must be present
+Scripting:
+pm.test("Content-Type is present", function () {
+pm.response.to.have.header("Content-Type");
+});
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful Login
+2.Successful Navigation
+3.The Response code must be 200 
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.Successful login
+2.Import request successful
+3.User must be able to perform SEND rrequest
+4.The user must be able delete booking id 2952 successfully if it is not previously deleted
+5.The status code must be 200</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 
+1.Successful Login
+2.Successful Navigation
+3.The Response code must be 500
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+1.Successful Login
+2.Successful Navigation
+3.The Response code must be 500
+</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1131,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -1126,11 +1214,78 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
@@ -1160,9 +1315,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1214,6 +1366,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1549,7 +1719,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4F09E5B-C095-4B12-8F0A-528D294F961A}">
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AA24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.88671875" customWidth="1"/>
@@ -1558,12 +1728,10 @@
     <col min="4" max="4" width="95.21875" customWidth="1"/>
     <col min="5" max="5" width="44.44140625" customWidth="1"/>
     <col min="6" max="6" width="24.33203125" customWidth="1"/>
-    <col min="7" max="7" width="19.44140625" customWidth="1"/>
-    <col min="8" max="8" width="30.33203125" customWidth="1"/>
-    <col min="9" max="9" width="25.33203125" customWidth="1"/>
+    <col min="7" max="7" width="25.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:27" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1585,38 +1753,34 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="2" spans="1:27" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="2"/>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-      <c r="F2" s="2"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-    </row>
-    <row r="3" spans="1:29" s="24" customFormat="1" ht="163.19999999999999" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A3" s="25"/>
-      <c r="B3" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="C3" s="27"/>
-      <c r="D3" s="26" t="s">
-        <v>136</v>
-      </c>
-      <c r="E3" s="26" t="s">
+    </row>
+    <row r="3" spans="1:27" s="23" customFormat="1" ht="163.19999999999999" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A3" s="24"/>
+      <c r="B3" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="26"/>
+      <c r="D3" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F3" s="32" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
@@ -1637,23 +1801,25 @@
       <c r="Y3" s="6"/>
       <c r="Z3" s="6"/>
       <c r="AA3" s="6"/>
-      <c r="AB3" s="6"/>
-      <c r="AC3" s="6"/>
-    </row>
-    <row r="4" spans="1:29" s="24" customFormat="1" ht="195" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="4" spans="1:27" s="23" customFormat="1" ht="195" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="7"/>
-      <c r="B4" s="26" t="s">
+      <c r="B4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="27"/>
-      <c r="D4" s="26" t="s">
+      <c r="C4" s="26"/>
+      <c r="D4" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="26" t="s">
+      <c r="E4" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
+      <c r="F4" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="G4" s="30" t="s">
+        <v>137</v>
+      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -1674,10 +1840,8 @@
       <c r="Y4" s="8"/>
       <c r="Z4" s="8"/>
       <c r="AA4" s="8"/>
-      <c r="AB4" s="8"/>
-      <c r="AC4" s="8"/>
-    </row>
-    <row r="5" spans="1:29" ht="223.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    </row>
+    <row r="5" spans="1:27" ht="223.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="7"/>
       <c r="B5" s="10" t="s">
         <v>10</v>
@@ -1686,425 +1850,376 @@
       <c r="D5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
-      <c r="I5" s="8"/>
-    </row>
-    <row r="6" spans="1:29" ht="8.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="9"/>
-      <c r="B6" s="11"/>
+      <c r="F5" s="34" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="266.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="7"/>
+      <c r="B6" s="10" t="s">
+        <v>13</v>
+      </c>
       <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:29" ht="266.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A7" s="7"/>
+      <c r="D6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E6" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="G6" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="258.60000000000002" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="9"/>
       <c r="B7" s="10" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C7" s="5"/>
       <c r="D7" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8"/>
-    </row>
-    <row r="8" spans="1:29" ht="258.60000000000002" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A8" s="9"/>
+        <v>17</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="269.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="7"/>
       <c r="B8" s="10" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:29" ht="269.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A9" s="7"/>
+        <v>20</v>
+      </c>
+      <c r="E8" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F8" s="34" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="9"/>
       <c r="B9" s="10" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C9" s="5"/>
       <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-    </row>
-    <row r="10" spans="1:29" ht="196.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A10" s="9"/>
+        <v>23</v>
+      </c>
+      <c r="E9" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="G9" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="244.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="7"/>
       <c r="B10" s="10" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F10" s="6"/>
-      <c r="G10" s="6"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:29" ht="244.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>26</v>
+      </c>
+      <c r="E10" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F10" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="G10" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="306" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="7"/>
       <c r="B11" s="10" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="C11" s="5"/>
       <c r="D11" s="4" t="s">
-        <v>26</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-    </row>
-    <row r="12" spans="1:29" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+      <c r="E11" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="G11" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="181.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="9"/>
-      <c r="B12" s="11"/>
+      <c r="B12" s="10" t="s">
+        <v>30</v>
+      </c>
       <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-      <c r="F12" s="6"/>
-      <c r="G12" s="6"/>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:29" ht="306" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="D12" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F12" s="32" t="s">
+        <v>143</v>
+      </c>
+      <c r="G12" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="198.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="7"/>
       <c r="B13" s="10" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C13" s="5"/>
       <c r="D13" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-    </row>
-    <row r="14" spans="1:29" ht="181.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>31</v>
+      </c>
+      <c r="E13" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F13" s="34" t="s">
+        <v>144</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="251.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="9"/>
       <c r="B14" s="10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="6"/>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:29" ht="198.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="E14" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="F14" s="32" t="s">
+        <v>145</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="265.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="7"/>
       <c r="B15" s="10" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="C15" s="5"/>
       <c r="D15" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-    </row>
-    <row r="16" spans="1:29" ht="251.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="9"/>
+        <v>39</v>
+      </c>
+      <c r="E15" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F15" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="G15" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="257.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7"/>
       <c r="B16" s="10" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="F16" s="6"/>
-      <c r="G16" s="6"/>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
-    </row>
-    <row r="17" spans="1:9" ht="265.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A17" s="7"/>
+        <v>42</v>
+      </c>
+      <c r="E16" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="G16" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="276" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="9"/>
       <c r="B17" s="10" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="C17" s="5"/>
       <c r="D17" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="G17" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" ht="216.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="7"/>
+      <c r="B18" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="C18" s="5"/>
+      <c r="D18" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E18" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
-      <c r="I17" s="8"/>
-    </row>
-    <row r="18" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="9"/>
-      <c r="B18" s="11"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-      <c r="F18" s="6"/>
-      <c r="G18" s="6"/>
-      <c r="H18" s="6"/>
-      <c r="I18" s="6"/>
-    </row>
-    <row r="19" spans="1:9" ht="257.39999999999998" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="7"/>
+      <c r="F18" s="34" t="s">
+        <v>146</v>
+      </c>
+      <c r="G18" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="187.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="9"/>
       <c r="B19" s="10" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C19" s="5"/>
       <c r="D19" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
-      <c r="I19" s="8"/>
-    </row>
-    <row r="20" spans="1:9" ht="276" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A20" s="9"/>
+        <v>49</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G19" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="220.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="7"/>
       <c r="B20" s="10" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C20" s="5"/>
       <c r="D20" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="F20" s="6"/>
-      <c r="G20" s="6"/>
-      <c r="H20" s="6"/>
-      <c r="I20" s="6"/>
-    </row>
-    <row r="21" spans="1:9" ht="216.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>49</v>
+      </c>
+      <c r="E20" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F20" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="G20" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" ht="409.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A21" s="7"/>
       <c r="B21" s="10" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="8"/>
-      <c r="H21" s="8"/>
-      <c r="I21" s="8"/>
-    </row>
-    <row r="22" spans="1:9" ht="187.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>53</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F21" s="34" t="s">
+        <v>148</v>
+      </c>
+      <c r="G21" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="409.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="9"/>
       <c r="B22" s="10" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-    </row>
-    <row r="23" spans="1:9" ht="220.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+        <v>56</v>
+      </c>
+      <c r="E22" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="G22" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" ht="274.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A23" s="7"/>
       <c r="B23" s="10" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="C23" s="5"/>
       <c r="D23" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="F23" s="8"/>
-      <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="9"/>
-      <c r="B24" s="11"/>
+        <v>59</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F23" s="34" t="s">
+        <v>150</v>
+      </c>
+      <c r="G23" s="30" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" ht="204.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="7"/>
+      <c r="B24" s="10" t="s">
+        <v>61</v>
+      </c>
       <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-    </row>
-    <row r="25" spans="1:9" ht="409.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="7"/>
-      <c r="B25" s="10" t="s">
-        <v>52</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="F25" s="8"/>
-      <c r="G25" s="8"/>
-      <c r="H25" s="8"/>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9" ht="409.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A26" s="9"/>
-      <c r="B26" s="10" t="s">
-        <v>55</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-    </row>
-    <row r="27" spans="1:9" ht="274.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A27" s="7"/>
-      <c r="B27" s="10" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="8"/>
-      <c r="G27" s="8"/>
-      <c r="H27" s="8"/>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" ht="409.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A28" s="9"/>
-      <c r="B28" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="4" t="s">
+      <c r="D24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E24" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-    </row>
-    <row r="29" spans="1:9" ht="409.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="7"/>
-      <c r="B29" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="8"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="9"/>
-      <c r="B30" s="11"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-      <c r="F30" s="6"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-    </row>
-    <row r="31" spans="1:9" ht="204.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A31" s="7"/>
-      <c r="B31" s="10" t="s">
-        <v>65</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="F31" s="8"/>
-      <c r="G31" s="8"/>
-      <c r="H31" s="8"/>
-      <c r="I31" s="8"/>
+      <c r="F24" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="G24" s="30" t="s">
+        <v>137</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2128,41 +2243,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="82.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
-        <v>89</v>
+      <c r="G1" s="16" t="s">
+        <v>85</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
-      <c r="K1" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>93</v>
+      <c r="K1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="17" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -2179,48 +2294,48 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="19" t="s">
-        <v>94</v>
+      <c r="N2" s="18" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="143.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="B3" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="E3" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="F3" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="G3" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="G3" s="12" t="s">
-        <v>74</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
       <c r="J3" s="6"/>
-      <c r="K3" s="12" t="s">
-        <v>138</v>
+      <c r="K3" s="11" t="s">
+        <v>134</v>
       </c>
       <c r="L3" s="6"/>
       <c r="M3" s="6"/>
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" ht="56.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>76</v>
+      <c r="A4" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>72</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2236,10 +2351,10 @@
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="A5" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="13">
         <v>-1</v>
       </c>
       <c r="C5" s="8"/>
@@ -2256,11 +2371,11 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>138</v>
+      <c r="A6" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>134</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -2276,11 +2391,11 @@
       <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="12" t="s">
-        <v>79</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>139</v>
+      <c r="A7" s="11" t="s">
+        <v>75</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>135</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2296,11 +2411,11 @@
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" ht="30" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B8" s="15" t="s">
-        <v>81</v>
+      <c r="A8" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="14" t="s">
+        <v>77</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -2316,11 +2431,11 @@
       <c r="N8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>140</v>
+      <c r="A9" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B9" s="13" t="s">
+        <v>136</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -2336,10 +2451,10 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="16">
+      <c r="A10" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B10" s="15">
         <v>0</v>
       </c>
       <c r="C10" s="8"/>
@@ -2356,11 +2471,11 @@
       <c r="N10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>85</v>
+      <c r="A11" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="B11" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -2376,11 +2491,11 @@
       <c r="N11" s="6"/>
     </row>
     <row r="12" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A12" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="B12" s="15" t="s">
-        <v>87</v>
+      <c r="A12" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="14" t="s">
+        <v>83</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -2396,10 +2511,10 @@
       <c r="N12" s="8"/>
     </row>
     <row r="13" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A13" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="B13" s="14">
+      <c r="A13" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="B13" s="13">
         <v>9.8765432345678895E+25</v>
       </c>
       <c r="C13" s="8"/>
@@ -2469,19 +2584,19 @@
         <v>5</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>89</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="20" t="s">
-        <v>93</v>
       </c>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
@@ -2513,8 +2628,8 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="21" t="s">
-        <v>94</v>
+      <c r="N2" s="20" t="s">
+        <v>90</v>
       </c>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -2532,10 +2647,10 @@
       <c r="AB2" s="2"/>
       <c r="AC2" s="2"/>
     </row>
-    <row r="3" spans="1:29" s="23" customFormat="1" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:29" s="22" customFormat="1" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6"/>
-      <c r="B3" s="22" t="s">
-        <v>96</v>
+      <c r="B3" s="21" t="s">
+        <v>92</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -2565,10 +2680,10 @@
       <c r="AB3" s="6"/>
       <c r="AC3" s="6"/>
     </row>
-    <row r="4" spans="1:29" s="23" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:29" s="22" customFormat="1" ht="18.600000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A4" s="8"/>
-      <c r="B4" s="22" t="s">
-        <v>98</v>
+      <c r="B4" s="21" t="s">
+        <v>94</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -2598,10 +2713,10 @@
       <c r="AB4" s="8"/>
       <c r="AC4" s="8"/>
     </row>
-    <row r="5" spans="1:29" s="23" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:29" s="22" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6"/>
-      <c r="B5" s="22" t="s">
-        <v>100</v>
+      <c r="B5" s="21" t="s">
+        <v>96</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -2631,10 +2746,10 @@
       <c r="AB5" s="6"/>
       <c r="AC5" s="6"/>
     </row>
-    <row r="6" spans="1:29" s="23" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:29" s="22" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="8"/>
-      <c r="B6" s="22" t="s">
-        <v>102</v>
+      <c r="B6" s="21" t="s">
+        <v>98</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -2664,10 +2779,10 @@
       <c r="AB6" s="8"/>
       <c r="AC6" s="8"/>
     </row>
-    <row r="7" spans="1:29" s="23" customFormat="1" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:29" s="22" customFormat="1" ht="19.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6"/>
-      <c r="B7" s="22" t="s">
-        <v>104</v>
+      <c r="B7" s="21" t="s">
+        <v>100</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -2697,10 +2812,10 @@
       <c r="AB7" s="6"/>
       <c r="AC7" s="6"/>
     </row>
-    <row r="8" spans="1:29" s="23" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:29" s="22" customFormat="1" ht="20.399999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="8"/>
-      <c r="B8" s="22" t="s">
-        <v>106</v>
+      <c r="B8" s="21" t="s">
+        <v>102</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -2730,10 +2845,10 @@
       <c r="AB8" s="8"/>
       <c r="AC8" s="8"/>
     </row>
-    <row r="9" spans="1:29" s="23" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:29" s="22" customFormat="1" ht="19.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
-      <c r="B9" s="22" t="s">
-        <v>108</v>
+      <c r="B9" s="21" t="s">
+        <v>104</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -2763,10 +2878,10 @@
       <c r="AB9" s="6"/>
       <c r="AC9" s="6"/>
     </row>
-    <row r="10" spans="1:29" s="23" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:29" s="22" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="8"/>
-      <c r="B10" s="22" t="s">
-        <v>110</v>
+      <c r="B10" s="21" t="s">
+        <v>106</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -2796,10 +2911,10 @@
       <c r="AB10" s="8"/>
       <c r="AC10" s="8"/>
     </row>
-    <row r="11" spans="1:29" s="23" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:29" s="22" customFormat="1" ht="16.8" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A11" s="6"/>
-      <c r="B11" s="22" t="s">
-        <v>111</v>
+      <c r="B11" s="21" t="s">
+        <v>107</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -2829,10 +2944,10 @@
       <c r="AB11" s="6"/>
       <c r="AC11" s="6"/>
     </row>
-    <row r="12" spans="1:29" s="23" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:29" s="22" customFormat="1" ht="23.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A12" s="8"/>
-      <c r="B12" s="22" t="s">
-        <v>113</v>
+      <c r="B12" s="21" t="s">
+        <v>109</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -2862,10 +2977,10 @@
       <c r="AB12" s="8"/>
       <c r="AC12" s="8"/>
     </row>
-    <row r="13" spans="1:29" s="23" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:29" s="22" customFormat="1" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A13" s="8"/>
       <c r="B13" s="8" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -2895,10 +3010,10 @@
       <c r="AB13" s="8"/>
       <c r="AC13" s="8"/>
     </row>
-    <row r="14" spans="1:29" s="23" customFormat="1" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:29" s="22" customFormat="1" ht="22.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
-      <c r="B14" s="22" t="s">
-        <v>115</v>
+      <c r="B14" s="21" t="s">
+        <v>111</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -2930,8 +3045,8 @@
     </row>
     <row r="15" spans="1:29" ht="25.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A15" s="8"/>
-      <c r="B15" s="22" t="s">
-        <v>116</v>
+      <c r="B15" s="21" t="s">
+        <v>112</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -2986,47 +3101,47 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:14" ht="82.2" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="J1" s="17" t="s">
+      <c r="J1" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="L1" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="M1" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="N1" s="17" t="s">
         <v>89</v>
-      </c>
-      <c r="K1" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="L1" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="M1" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="N1" s="18" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="2" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
@@ -3043,16 +3158,16 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="19" t="s">
-        <v>94</v>
+      <c r="N2" s="18" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="3" spans="1:14" ht="49.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="B3" s="28" t="s">
-        <v>96</v>
+      <c r="A3" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="B3" s="27" t="s">
+        <v>92</v>
       </c>
       <c r="C3" s="8"/>
       <c r="D3" s="8"/>
@@ -3068,11 +3183,11 @@
       <c r="N3" s="6"/>
     </row>
     <row r="4" spans="1:14" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>98</v>
+      <c r="A4" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>94</v>
       </c>
       <c r="C4" s="8"/>
       <c r="D4" s="8"/>
@@ -3088,11 +3203,11 @@
       <c r="N4" s="8"/>
     </row>
     <row r="5" spans="1:14" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>100</v>
+      <c r="A5" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>96</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="8"/>
@@ -3108,11 +3223,11 @@
       <c r="N5" s="6"/>
     </row>
     <row r="6" spans="1:14" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>102</v>
+      <c r="A6" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>98</v>
       </c>
       <c r="C6" s="8"/>
       <c r="D6" s="8"/>
@@ -3128,11 +3243,11 @@
       <c r="N6" s="8"/>
     </row>
     <row r="7" spans="1:14" ht="35.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>104</v>
+      <c r="A7" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>100</v>
       </c>
       <c r="C7" s="8"/>
       <c r="D7" s="8"/>
@@ -3148,11 +3263,11 @@
       <c r="N7" s="6"/>
     </row>
     <row r="8" spans="1:14" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="B8" s="13" t="s">
-        <v>106</v>
+      <c r="A8" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>102</v>
       </c>
       <c r="C8" s="8"/>
       <c r="D8" s="8"/>
@@ -3168,11 +3283,11 @@
       <c r="N8" s="8"/>
     </row>
     <row r="9" spans="1:14" ht="57" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A9" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B9" s="13" t="s">
-        <v>108</v>
+      <c r="A9" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>104</v>
       </c>
       <c r="C9" s="8"/>
       <c r="D9" s="8"/>
@@ -3188,11 +3303,11 @@
       <c r="N9" s="6"/>
     </row>
     <row r="10" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A10" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="13" t="s">
-        <v>110</v>
+      <c r="A10" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>106</v>
       </c>
       <c r="C10" s="8"/>
       <c r="D10" s="8"/>
@@ -3208,11 +3323,11 @@
       <c r="N10" s="8"/>
     </row>
     <row r="11" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="A11" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="B11" s="13" t="s">
-        <v>113</v>
+      <c r="A11" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>109</v>
       </c>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
@@ -3229,8 +3344,8 @@
     </row>
     <row r="12" spans="1:14" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A12" s="8"/>
-      <c r="B12" s="13" t="s">
-        <v>114</v>
+      <c r="B12" s="12" t="s">
+        <v>110</v>
       </c>
       <c r="C12" s="8"/>
       <c r="D12" s="8"/>
@@ -3247,8 +3362,8 @@
     </row>
     <row r="13" spans="1:14" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A13" s="6"/>
-      <c r="B13" s="13" t="s">
-        <v>115</v>
+      <c r="B13" s="12" t="s">
+        <v>111</v>
       </c>
       <c r="C13" s="8"/>
       <c r="D13" s="8"/>
@@ -3265,8 +3380,8 @@
     </row>
     <row r="14" spans="1:14" ht="34.200000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A14" s="8"/>
-      <c r="B14" s="13" t="s">
-        <v>116</v>
+      <c r="B14" s="12" t="s">
+        <v>112</v>
       </c>
       <c r="C14" s="8"/>
       <c r="D14" s="8"/>
@@ -3283,8 +3398,8 @@
     </row>
     <row r="15" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="6"/>
-      <c r="B15" s="12" t="s">
-        <v>117</v>
+      <c r="B15" s="11" t="s">
+        <v>113</v>
       </c>
       <c r="C15" s="8"/>
       <c r="D15" s="8"/>
@@ -3301,8 +3416,8 @@
     </row>
     <row r="16" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A16" s="8"/>
-      <c r="B16" s="13" t="s">
-        <v>118</v>
+      <c r="B16" s="12" t="s">
+        <v>114</v>
       </c>
       <c r="C16" s="8"/>
       <c r="D16" s="8"/>
@@ -3319,8 +3434,8 @@
     </row>
     <row r="17" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A17" s="6"/>
-      <c r="B17" s="12" t="s">
-        <v>119</v>
+      <c r="B17" s="11" t="s">
+        <v>115</v>
       </c>
       <c r="C17" s="8"/>
       <c r="D17" s="8"/>
@@ -3337,8 +3452,8 @@
     </row>
     <row r="18" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A18" s="8"/>
-      <c r="B18" s="13" t="s">
-        <v>120</v>
+      <c r="B18" s="12" t="s">
+        <v>116</v>
       </c>
       <c r="C18" s="8"/>
       <c r="D18" s="8"/>
@@ -3355,8 +3470,8 @@
     </row>
     <row r="19" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A19" s="6"/>
-      <c r="B19" s="13" t="s">
-        <v>121</v>
+      <c r="B19" s="12" t="s">
+        <v>117</v>
       </c>
       <c r="C19" s="8"/>
       <c r="D19" s="8"/>
@@ -3373,8 +3488,8 @@
     </row>
     <row r="20" spans="1:14" ht="29.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A20" s="8"/>
-      <c r="B20" s="13" t="s">
-        <v>122</v>
+      <c r="B20" s="12" t="s">
+        <v>118</v>
       </c>
       <c r="C20" s="8"/>
       <c r="D20" s="8"/>
@@ -3391,8 +3506,8 @@
     </row>
     <row r="21" spans="1:14" ht="32.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A21" s="6"/>
-      <c r="B21" s="13" t="s">
-        <v>123</v>
+      <c r="B21" s="12" t="s">
+        <v>119</v>
       </c>
       <c r="C21" s="8"/>
       <c r="D21" s="8"/>
@@ -3409,8 +3524,8 @@
     </row>
     <row r="22" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A22" s="8"/>
-      <c r="B22" s="13" t="s">
-        <v>124</v>
+      <c r="B22" s="12" t="s">
+        <v>120</v>
       </c>
       <c r="C22" s="8"/>
       <c r="D22" s="8"/>
@@ -3427,8 +3542,8 @@
     </row>
     <row r="23" spans="1:14" ht="39.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="6"/>
-      <c r="B23" s="13" t="s">
-        <v>125</v>
+      <c r="B23" s="12" t="s">
+        <v>121</v>
       </c>
       <c r="C23" s="8"/>
       <c r="D23" s="8"/>
@@ -3445,8 +3560,8 @@
     </row>
     <row r="24" spans="1:14" ht="37.799999999999997" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A24" s="8"/>
-      <c r="B24" s="13" t="s">
-        <v>126</v>
+      <c r="B24" s="12" t="s">
+        <v>122</v>
       </c>
       <c r="C24" s="8"/>
       <c r="D24" s="8"/>
@@ -3463,8 +3578,8 @@
     </row>
     <row r="25" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A25" s="6"/>
-      <c r="B25" s="13" t="s">
-        <v>87</v>
+      <c r="B25" s="12" t="s">
+        <v>83</v>
       </c>
       <c r="C25" s="8"/>
       <c r="D25" s="8"/>
@@ -3481,8 +3596,8 @@
     </row>
     <row r="26" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A26" s="8"/>
-      <c r="B26" s="13" t="s">
-        <v>127</v>
+      <c r="B26" s="12" t="s">
+        <v>123</v>
       </c>
       <c r="C26" s="8"/>
       <c r="D26" s="8"/>
@@ -3499,8 +3614,8 @@
     </row>
     <row r="27" spans="1:14" ht="33.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A27" s="6"/>
-      <c r="B27" s="13" t="s">
-        <v>128</v>
+      <c r="B27" s="12" t="s">
+        <v>124</v>
       </c>
       <c r="C27" s="8"/>
       <c r="D27" s="8"/>
@@ -3517,8 +3632,8 @@
     </row>
     <row r="28" spans="1:14" ht="36.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A28" s="8"/>
-      <c r="B28" s="13" t="s">
-        <v>129</v>
+      <c r="B28" s="12" t="s">
+        <v>125</v>
       </c>
       <c r="C28" s="8"/>
       <c r="D28" s="8"/>
@@ -3533,10 +3648,10 @@
       <c r="M28" s="8"/>
       <c r="N28" s="8"/>
     </row>
-    <row r="29" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="29" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A29" s="6"/>
-      <c r="B29" s="13" t="s">
-        <v>130</v>
+      <c r="B29" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="C29" s="8"/>
       <c r="D29" s="8"/>
@@ -3553,8 +3668,8 @@
     </row>
     <row r="30" spans="1:14" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A30" s="8"/>
-      <c r="B30" s="13" t="s">
-        <v>131</v>
+      <c r="B30" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="C30" s="8"/>
       <c r="D30" s="8"/>
@@ -3569,10 +3684,10 @@
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
     </row>
-    <row r="31" spans="1:14" ht="41.4" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="31" spans="1:14" ht="21" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A31" s="6"/>
-      <c r="B31" s="13" t="s">
-        <v>132</v>
+      <c r="B31" s="12" t="s">
+        <v>128</v>
       </c>
       <c r="C31" s="8"/>
       <c r="D31" s="8"/>
@@ -3589,8 +3704,8 @@
     </row>
     <row r="32" spans="1:14" ht="43.8" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A32" s="8"/>
-      <c r="B32" s="13" t="s">
-        <v>133</v>
+      <c r="B32" s="12" t="s">
+        <v>129</v>
       </c>
       <c r="C32" s="8"/>
       <c r="D32" s="8"/>
@@ -3607,8 +3722,8 @@
     </row>
     <row r="33" spans="1:14" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A33" s="6"/>
-      <c r="B33" s="13" t="s">
-        <v>134</v>
+      <c r="B33" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="C33" s="8"/>
       <c r="D33" s="8"/>
